--- a/BugReport(Guvi).xlsx
+++ b/BugReport(Guvi).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Monika Devi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuviHackathonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEB4379-CFC8-4794-A0F0-3BC51709C016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C111D2DD-E05D-45B3-8526-0970F3AB445C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1281EEA7-3831-4BE5-B9F5-C8D6B5081212}"/>
   </bookViews>
@@ -108,13 +108,13 @@
     <t>"view report" button should not be clickable</t>
   </si>
   <si>
-    <t>"view report" button should is clickable</t>
-  </si>
-  <si>
     <t>View report should not be clickable for upcoming and ongoing test</t>
   </si>
   <si>
     <t>Medium</t>
+  </si>
+  <si>
+    <t>"view report" button is clickable</t>
   </si>
 </sst>
 </file>
@@ -579,16 +579,16 @@
         <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
